--- a/outputs/energy_intelligence_reports.xlsx
+++ b/outputs/energy_intelligence_reports.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-17 12:22</t>
+          <t>2026-07-17 12:26</t>
         </is>
       </c>
     </row>

--- a/outputs/energy_intelligence_reports.xlsx
+++ b/outputs/energy_intelligence_reports.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-17 12:26</t>
+          <t>2026-07-18 06:07</t>
         </is>
       </c>
     </row>

--- a/outputs/energy_intelligence_reports.xlsx
+++ b/outputs/energy_intelligence_reports.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-18 06:07</t>
+          <t>2026-08-05 03:56</t>
         </is>
       </c>
     </row>
@@ -1483,20 +1483,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Building_17</t>
+          <t>Building_3</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>107951.5</v>
+        <v>172419.79</v>
       </c>
       <c r="C39" t="n">
-        <v>19.34</v>
+        <v>30.83</v>
       </c>
       <c r="D39" t="n">
-        <v>6.47</v>
+        <v>10.33</v>
       </c>
       <c r="E39" t="n">
-        <v>31.86</v>
+        <v>31.92</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1507,20 +1507,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Building_3</t>
+          <t>Building_21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>172419.79</v>
+        <v>114274.72</v>
       </c>
       <c r="C40" t="n">
-        <v>30.83</v>
+        <v>20.4</v>
       </c>
       <c r="D40" t="n">
-        <v>10.33</v>
+        <v>6.85</v>
       </c>
       <c r="E40" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1531,20 +1531,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Building_21</t>
+          <t>Building_28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>114274.72</v>
+        <v>103716.73</v>
       </c>
       <c r="C41" t="n">
-        <v>20.4</v>
+        <v>18.5</v>
       </c>
       <c r="D41" t="n">
-        <v>6.85</v>
+        <v>6.22</v>
       </c>
       <c r="E41" t="n">
-        <v>31.97</v>
+        <v>32</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1555,20 +1555,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Building_28</t>
+          <t>Building_35</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>103716.73</v>
+        <v>143241.09</v>
       </c>
       <c r="C42" t="n">
-        <v>18.5</v>
+        <v>25.54</v>
       </c>
       <c r="D42" t="n">
-        <v>6.22</v>
+        <v>8.58</v>
       </c>
       <c r="E42" t="n">
-        <v>32</v>
+        <v>32.01</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1579,20 +1579,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Building_35</t>
+          <t>Building_1</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>143241.09</v>
+        <v>167256.9</v>
       </c>
       <c r="C43" t="n">
-        <v>25.54</v>
+        <v>29.81</v>
       </c>
       <c r="D43" t="n">
-        <v>8.58</v>
+        <v>10.03</v>
       </c>
       <c r="E43" t="n">
-        <v>32.01</v>
+        <v>32.02</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1603,20 +1603,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Building_1</t>
+          <t>Building_37</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>167256.9</v>
+        <v>150555.21</v>
       </c>
       <c r="C44" t="n">
-        <v>29.81</v>
+        <v>26.83</v>
       </c>
       <c r="D44" t="n">
-        <v>10.03</v>
+        <v>9.02</v>
       </c>
       <c r="E44" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1627,20 +1627,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Building_37</t>
+          <t>Building_31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>150555.21</v>
+        <v>188357.57</v>
       </c>
       <c r="C45" t="n">
-        <v>26.83</v>
+        <v>33.48</v>
       </c>
       <c r="D45" t="n">
-        <v>9.02</v>
+        <v>11.29</v>
       </c>
       <c r="E45" t="n">
-        <v>32.03</v>
+        <v>32.11</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1651,20 +1651,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Building_31</t>
+          <t>Building_49</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>188357.57</v>
+        <v>146527.52</v>
       </c>
       <c r="C46" t="n">
-        <v>33.48</v>
+        <v>26.03</v>
       </c>
       <c r="D46" t="n">
-        <v>11.29</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>32.11</v>
+        <v>32.13</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1675,20 +1675,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Building_49</t>
+          <t>Building_38</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>146527.52</v>
+        <v>118832.81</v>
       </c>
       <c r="C47" t="n">
-        <v>26.03</v>
+        <v>21.01</v>
       </c>
       <c r="D47" t="n">
-        <v>8.779999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="E47" t="n">
-        <v>32.13</v>
+        <v>32.28</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1699,20 +1699,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Building_38</t>
+          <t>Building_6</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>118832.81</v>
+        <v>98056.91</v>
       </c>
       <c r="C48" t="n">
-        <v>21.01</v>
+        <v>17.33</v>
       </c>
       <c r="D48" t="n">
-        <v>7.12</v>
+        <v>5.88</v>
       </c>
       <c r="E48" t="n">
-        <v>32.28</v>
+        <v>32.3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1723,20 +1723,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Building_6</t>
+          <t>Building_50</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>98056.91</v>
+        <v>161719.33</v>
       </c>
       <c r="C49" t="n">
-        <v>17.33</v>
+        <v>28.46</v>
       </c>
       <c r="D49" t="n">
-        <v>5.88</v>
+        <v>9.69</v>
       </c>
       <c r="E49" t="n">
-        <v>32.3</v>
+        <v>32.43</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1747,20 +1747,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Building_50</t>
+          <t>Building_25</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>161719.33</v>
+        <v>148035.08</v>
       </c>
       <c r="C50" t="n">
-        <v>28.46</v>
+        <v>25.99</v>
       </c>
       <c r="D50" t="n">
-        <v>9.69</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>32.43</v>
+        <v>32.51</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1771,24 +1771,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Building_25</t>
+          <t>Building_17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>148035.08</v>
+        <v>134945.97</v>
       </c>
       <c r="C51" t="n">
-        <v>25.99</v>
+        <v>4.82</v>
       </c>
       <c r="D51" t="n">
-        <v>8.869999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="E51" t="n">
-        <v>32.51</v>
+        <v>142.26</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inefficient</t>
+          <t>Efficient</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 09:45:00</t>
+          <t>Weekend waste detected at 2023-01-01 09:30:00</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 09:30:00</t>
+          <t>Weekend waste detected at 2023-01-01 10:00:00</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 10:00:00</t>
+          <t>Weekend waste detected at 2023-01-01 09:45:00</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 08:00:00</t>
+          <t>Weekend waste detected at 2023-01-01 08:45:00</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 08:45:00</t>
+          <t>Weekend waste detected at 2023-01-01 08:00:00</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 10:15:00</t>
+          <t>Weekend waste detected at 2023-01-01 09:30:00</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 09:00:00</t>
+          <t>Weekend waste detected at 2023-01-01 10:15:00</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2504,7 +2504,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Building_17</t>
+          <t>Building_42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 09:15:00</t>
+          <t>Weekend waste detected at 2023-01-01 08:15:00</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 08:15:00</t>
+          <t>Weekend waste detected at 2023-01-01 09:00:00</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2603,7 +2603,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Building_17</t>
+          <t>Building_42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2618,11 +2618,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 09:30:00</t>
+          <t>Weekend waste detected at 2023-01-01 08:45:00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,11 +2651,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 09:30:00</t>
+          <t>Weekend waste detected at 2023-01-01 08:30:00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Building_17</t>
+          <t>Building_42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2684,11 +2684,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Weekend waste detected at 2023-01-01 10:00:00</t>
+          <t>Weekend waste detected at 2023-01-01 08:00:00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,336 +2696,6 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>46201.36074645224</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Building_17</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>weekend_waste</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Weekend waste detected at 2023-01-01 08:00:00</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>46201.36074645224</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Building_42</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>weekend_waste</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Weekend waste detected at 2023-01-01 08:45:00</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>46201.36074645224</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Building_17</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>weekend_waste</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Weekend waste detected at 2023-01-01 09:45:00</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>46201.36074645224</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Building_17</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>weekend_waste</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Weekend waste detected at 2023-01-01 09:00:00</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>46201.36074645224</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Building_42</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>weekend_waste</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Weekend waste detected at 2023-01-01 08:30:00</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>46201.36074645224</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Building_17</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>weekend_waste</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Weekend waste detected at 2023-01-01 08:15:00</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>46201.36074645224</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Building_42</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>weekend_waste</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Weekend waste detected at 2023-01-01 08:00:00</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>46201.36074645224</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Building_17</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>weekend_waste</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Weekend waste detected at 2023-01-01 08:30:00</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>46201.36074645224</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Building_17</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>weekend_waste</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Weekend waste detected at 2023-01-01 10:15:00</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>46201.36074645224</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Building_17</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>weekend_waste</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Weekend waste detected at 2023-01-01 08:45:00</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n">
         <v>46201.36074645224</v>
       </c>
     </row>
@@ -3040,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4090,273 +3760,247 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Building_17</t>
+          <t>Building_29</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>2023</v>
       </c>
       <c r="C81" t="n">
-        <v>1397.55</v>
+        <v>1381.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Building_17</t>
+          <t>Building_48</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C82" t="n">
-        <v>1386.3</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Building_29</t>
+          <t>Building_48</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C83" t="n">
-        <v>1381.5</v>
+        <v>1274.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Building_48</t>
+          <t>Building_28</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2023</v>
       </c>
       <c r="C84" t="n">
-        <v>1278</v>
+        <v>1182.75</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Building_48</t>
+          <t>Building_28</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>2024</v>
       </c>
       <c r="C85" t="n">
-        <v>1274.1</v>
+        <v>1177.05</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Building_28</t>
+          <t>Building_16</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2023</v>
       </c>
       <c r="C86" t="n">
-        <v>1182.75</v>
+        <v>1105.65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Building_28</t>
+          <t>Building_16</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>2024</v>
       </c>
       <c r="C87" t="n">
-        <v>1177.05</v>
+        <v>1105.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Building_16</t>
+          <t>Building_6</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>2023</v>
       </c>
       <c r="C88" t="n">
-        <v>1105.65</v>
+        <v>878.25</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Building_16</t>
+          <t>Building_6</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>2024</v>
       </c>
       <c r="C89" t="n">
-        <v>1105.5</v>
+        <v>868.2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Building_6</t>
+          <t>Building_39</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>2023</v>
       </c>
       <c r="C90" t="n">
-        <v>878.25</v>
+        <v>831</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Building_6</t>
+          <t>Building_39</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>2024</v>
       </c>
       <c r="C91" t="n">
-        <v>868.2</v>
+        <v>829.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Building_39</t>
+          <t>Building_46</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C92" t="n">
-        <v>831</v>
+        <v>768.45</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Building_39</t>
+          <t>Building_46</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C93" t="n">
-        <v>829.5</v>
+        <v>765.9</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Building_46</t>
+          <t>Building_43</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>2024</v>
       </c>
       <c r="C94" t="n">
-        <v>768.45</v>
+        <v>698.55</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Building_46</t>
+          <t>Building_43</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>2023</v>
       </c>
       <c r="C95" t="n">
-        <v>765.9</v>
+        <v>697.65</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Building_43</t>
+          <t>Building_26</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C96" t="n">
-        <v>698.55</v>
+        <v>625.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Building_43</t>
+          <t>Building_26</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C97" t="n">
-        <v>697.65</v>
+        <v>618.75</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Building_26</t>
+          <t>Building_44</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C98" t="n">
-        <v>625.5</v>
+        <v>616.05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Building_26</t>
+          <t>Building_44</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C99" t="n">
-        <v>618.75</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Building_44</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C100" t="n">
-        <v>616.05</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Building_44</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C101" t="n">
         <v>609.75</v>
       </c>
     </row>
@@ -4371,7 +4015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6125,23 +5769,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Building_17</t>
+          <t>Building_29</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>2024</v>
       </c>
       <c r="C80" t="n">
-        <v>6486.97</v>
+        <v>6473.26</v>
       </c>
       <c r="D80" t="n">
-        <v>1386.3</v>
+        <v>1399.5</v>
       </c>
       <c r="E80" t="n">
         <v>912.5</v>
       </c>
       <c r="F80" t="n">
-        <v>8785.77</v>
+        <v>8785.26</v>
       </c>
     </row>
     <row r="81">
@@ -6151,458 +5795,414 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C81" t="n">
-        <v>6473.26</v>
+        <v>6457.33</v>
       </c>
       <c r="D81" t="n">
-        <v>1399.5</v>
+        <v>1381.5</v>
       </c>
       <c r="E81" t="n">
         <v>912.5</v>
       </c>
       <c r="F81" t="n">
-        <v>8785.26</v>
+        <v>8751.33</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Building_17</t>
+          <t>Building_48</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C82" t="n">
-        <v>6467.21</v>
+        <v>6344.78</v>
       </c>
       <c r="D82" t="n">
-        <v>1397.55</v>
+        <v>1274.1</v>
       </c>
       <c r="E82" t="n">
         <v>912.5</v>
       </c>
       <c r="F82" t="n">
-        <v>8777.26</v>
+        <v>8531.379999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Building_29</t>
+          <t>Building_48</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2023</v>
       </c>
       <c r="C83" t="n">
-        <v>6457.33</v>
+        <v>6335.98</v>
       </c>
       <c r="D83" t="n">
-        <v>1381.5</v>
+        <v>1278</v>
       </c>
       <c r="E83" t="n">
         <v>912.5</v>
       </c>
       <c r="F83" t="n">
-        <v>8751.33</v>
+        <v>8526.48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Building_48</t>
+          <t>Building_28</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2024</v>
       </c>
       <c r="C84" t="n">
-        <v>6344.78</v>
+        <v>6232.09</v>
       </c>
       <c r="D84" t="n">
-        <v>1274.1</v>
+        <v>1177.05</v>
       </c>
       <c r="E84" t="n">
         <v>912.5</v>
       </c>
       <c r="F84" t="n">
-        <v>8531.379999999999</v>
+        <v>8321.639999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Building_48</t>
+          <t>Building_28</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>2023</v>
       </c>
       <c r="C85" t="n">
-        <v>6335.98</v>
+        <v>6213.92</v>
       </c>
       <c r="D85" t="n">
-        <v>1278</v>
+        <v>1182.75</v>
       </c>
       <c r="E85" t="n">
         <v>912.5</v>
       </c>
       <c r="F85" t="n">
-        <v>8526.48</v>
+        <v>8309.17</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Building_28</t>
+          <t>Building_16</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2024</v>
       </c>
       <c r="C86" t="n">
-        <v>6232.09</v>
+        <v>6167.79</v>
       </c>
       <c r="D86" t="n">
-        <v>1177.05</v>
+        <v>1105.5</v>
       </c>
       <c r="E86" t="n">
         <v>912.5</v>
       </c>
       <c r="F86" t="n">
-        <v>8321.639999999999</v>
+        <v>8185.79</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Building_28</t>
+          <t>Building_16</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>2023</v>
       </c>
       <c r="C87" t="n">
-        <v>6213.92</v>
+        <v>6152.85</v>
       </c>
       <c r="D87" t="n">
-        <v>1182.75</v>
+        <v>1105.65</v>
       </c>
       <c r="E87" t="n">
         <v>912.5</v>
       </c>
       <c r="F87" t="n">
-        <v>8309.17</v>
+        <v>8171</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Building_16</t>
+          <t>Building_6</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>2024</v>
       </c>
       <c r="C88" t="n">
-        <v>6167.79</v>
+        <v>5892.47</v>
       </c>
       <c r="D88" t="n">
-        <v>1105.5</v>
+        <v>868.2</v>
       </c>
       <c r="E88" t="n">
         <v>912.5</v>
       </c>
       <c r="F88" t="n">
-        <v>8185.79</v>
+        <v>7673.17</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Building_16</t>
+          <t>Building_6</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>6152.85</v>
+        <v>5874.36</v>
       </c>
       <c r="D89" t="n">
-        <v>1105.65</v>
+        <v>878.25</v>
       </c>
       <c r="E89" t="n">
         <v>912.5</v>
       </c>
       <c r="F89" t="n">
-        <v>8171</v>
+        <v>7665.11</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Building_6</t>
+          <t>Building_39</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>5892.47</v>
+        <v>5844.17</v>
       </c>
       <c r="D90" t="n">
-        <v>868.2</v>
+        <v>829.5</v>
       </c>
       <c r="E90" t="n">
         <v>912.5</v>
       </c>
       <c r="F90" t="n">
-        <v>7673.17</v>
+        <v>7586.17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Building_6</t>
+          <t>Building_39</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>2023</v>
       </c>
       <c r="C91" t="n">
-        <v>5874.36</v>
+        <v>5825.61</v>
       </c>
       <c r="D91" t="n">
-        <v>878.25</v>
+        <v>831</v>
       </c>
       <c r="E91" t="n">
         <v>912.5</v>
       </c>
       <c r="F91" t="n">
-        <v>7665.11</v>
+        <v>7569.11</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Building_39</t>
+          <t>Building_46</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>2024</v>
       </c>
       <c r="C92" t="n">
-        <v>5844.17</v>
+        <v>5771.09</v>
       </c>
       <c r="D92" t="n">
-        <v>829.5</v>
+        <v>768.45</v>
       </c>
       <c r="E92" t="n">
         <v>912.5</v>
       </c>
       <c r="F92" t="n">
-        <v>7586.17</v>
+        <v>7452.04</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Building_39</t>
+          <t>Building_46</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>2023</v>
       </c>
       <c r="C93" t="n">
-        <v>5825.61</v>
+        <v>5746.23</v>
       </c>
       <c r="D93" t="n">
-        <v>831</v>
+        <v>765.9</v>
       </c>
       <c r="E93" t="n">
         <v>912.5</v>
       </c>
       <c r="F93" t="n">
-        <v>7569.11</v>
+        <v>7424.63</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Building_46</t>
+          <t>Building_43</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>2024</v>
       </c>
       <c r="C94" t="n">
-        <v>5771.09</v>
+        <v>5692.94</v>
       </c>
       <c r="D94" t="n">
-        <v>768.45</v>
+        <v>698.55</v>
       </c>
       <c r="E94" t="n">
         <v>912.5</v>
       </c>
       <c r="F94" t="n">
-        <v>7452.04</v>
+        <v>7303.99</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Building_46</t>
+          <t>Building_43</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>2023</v>
       </c>
       <c r="C95" t="n">
-        <v>5746.23</v>
+        <v>5677.64</v>
       </c>
       <c r="D95" t="n">
-        <v>765.9</v>
+        <v>697.65</v>
       </c>
       <c r="E95" t="n">
         <v>912.5</v>
       </c>
       <c r="F95" t="n">
-        <v>7424.63</v>
+        <v>7287.79</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Building_43</t>
+          <t>Building_26</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>2024</v>
       </c>
       <c r="C96" t="n">
-        <v>5692.94</v>
+        <v>5618.47</v>
       </c>
       <c r="D96" t="n">
-        <v>698.55</v>
+        <v>618.75</v>
       </c>
       <c r="E96" t="n">
         <v>912.5</v>
       </c>
       <c r="F96" t="n">
-        <v>7303.99</v>
+        <v>7149.72</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Building_43</t>
+          <t>Building_26</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>2023</v>
       </c>
       <c r="C97" t="n">
-        <v>5677.64</v>
+        <v>5599.08</v>
       </c>
       <c r="D97" t="n">
-        <v>697.65</v>
+        <v>625.5</v>
       </c>
       <c r="E97" t="n">
         <v>912.5</v>
       </c>
       <c r="F97" t="n">
-        <v>7287.79</v>
+        <v>7137.08</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Building_26</t>
+          <t>Building_44</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>2024</v>
       </c>
       <c r="C98" t="n">
-        <v>5618.47</v>
+        <v>5605.74</v>
       </c>
       <c r="D98" t="n">
-        <v>618.75</v>
+        <v>616.05</v>
       </c>
       <c r="E98" t="n">
         <v>912.5</v>
       </c>
       <c r="F98" t="n">
-        <v>7149.72</v>
+        <v>7134.29</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Building_26</t>
+          <t>Building_44</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>2023</v>
       </c>
       <c r="C99" t="n">
-        <v>5599.08</v>
+        <v>5586.53</v>
       </c>
       <c r="D99" t="n">
-        <v>625.5</v>
+        <v>609.75</v>
       </c>
       <c r="E99" t="n">
         <v>912.5</v>
       </c>
       <c r="F99" t="n">
-        <v>7137.08</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Building_44</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C100" t="n">
-        <v>5605.74</v>
-      </c>
-      <c r="D100" t="n">
-        <v>616.05</v>
-      </c>
-      <c r="E100" t="n">
-        <v>912.5</v>
-      </c>
-      <c r="F100" t="n">
-        <v>7134.29</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Building_44</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C101" t="n">
-        <v>5586.53</v>
-      </c>
-      <c r="D101" t="n">
-        <v>609.75</v>
-      </c>
-      <c r="E101" t="n">
-        <v>912.5</v>
-      </c>
-      <c r="F101" t="n">
         <v>7108.78</v>
       </c>
     </row>
@@ -6634,386 +6234,386 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>45657.04166666666</v>
+        <v>45658.03125</v>
       </c>
       <c r="B2" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>45657.08333333334</v>
+        <v>45658.07291666666</v>
       </c>
       <c r="B3" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>45657.125</v>
+        <v>45658.11458333334</v>
       </c>
       <c r="B4" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>45657.16666666666</v>
+        <v>45658.15625</v>
       </c>
       <c r="B5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>45657.20833333334</v>
+        <v>45658.19791666666</v>
       </c>
       <c r="B6" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>45657.25</v>
+        <v>45658.23958333334</v>
       </c>
       <c r="B7" t="n">
-        <v>1.59</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>45657.29166666666</v>
+        <v>45658.28125</v>
       </c>
       <c r="B8" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>45657.33333333334</v>
+        <v>45658.32291666666</v>
       </c>
       <c r="B9" t="n">
-        <v>2.44</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>45657.375</v>
+        <v>45658.36458333334</v>
       </c>
       <c r="B10" t="n">
-        <v>2.7</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>45657.41666666666</v>
+        <v>45658.40625</v>
       </c>
       <c r="B11" t="n">
-        <v>2.83</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>45657.45833333334</v>
+        <v>45658.44791666666</v>
       </c>
       <c r="B12" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>45657.5</v>
+        <v>45658.48958333334</v>
       </c>
       <c r="B13" t="n">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>45657.54166666666</v>
+        <v>45658.53125</v>
       </c>
       <c r="B14" t="n">
-        <v>2.93</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>45657.58333333334</v>
+        <v>45658.57291666666</v>
       </c>
       <c r="B15" t="n">
-        <v>2.98</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>45657.625</v>
+        <v>45658.61458333334</v>
       </c>
       <c r="B16" t="n">
-        <v>3.09</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>45657.66666666666</v>
+        <v>45658.65625</v>
       </c>
       <c r="B17" t="n">
-        <v>3.23</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>45657.70833333334</v>
+        <v>45658.69791666666</v>
       </c>
       <c r="B18" t="n">
-        <v>3.29</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>45657.75</v>
+        <v>45658.73958333334</v>
       </c>
       <c r="B19" t="n">
-        <v>3.15</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>45657.79166666666</v>
+        <v>45658.78125</v>
       </c>
       <c r="B20" t="n">
-        <v>2.72</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>45657.83333333334</v>
+        <v>45658.82291666666</v>
       </c>
       <c r="B21" t="n">
-        <v>2.09</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>45657.875</v>
+        <v>45658.86458333334</v>
       </c>
       <c r="B22" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>45657.91666666666</v>
+        <v>45658.90625</v>
       </c>
       <c r="B23" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>45657.95833333334</v>
+        <v>45658.94791666666</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>45658</v>
+        <v>45658.98958333334</v>
       </c>
       <c r="B25" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>45658.04166666666</v>
+        <v>45659.03125</v>
       </c>
       <c r="B26" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>45658.08333333334</v>
+        <v>45659.07291666666</v>
       </c>
       <c r="B27" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>45658.125</v>
+        <v>45659.11458333334</v>
       </c>
       <c r="B28" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>45658.16666666666</v>
+        <v>45659.15625</v>
       </c>
       <c r="B29" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>45658.20833333334</v>
+        <v>45659.19791666666</v>
       </c>
       <c r="B30" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>45658.25</v>
+        <v>45659.23958333334</v>
       </c>
       <c r="B31" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>45658.29166666666</v>
+        <v>45659.28125</v>
       </c>
       <c r="B32" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>45658.33333333334</v>
+        <v>45659.32291666666</v>
       </c>
       <c r="B33" t="n">
-        <v>2.39</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>45658.375</v>
+        <v>45659.36458333334</v>
       </c>
       <c r="B34" t="n">
-        <v>2.66</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>45658.41666666666</v>
+        <v>45659.40625</v>
       </c>
       <c r="B35" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>45658.45833333334</v>
+        <v>45659.44791666666</v>
       </c>
       <c r="B36" t="n">
-        <v>2.86</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>45658.5</v>
+        <v>45659.48958333334</v>
       </c>
       <c r="B37" t="n">
-        <v>2.89</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>45658.54166666666</v>
+        <v>45659.53125</v>
       </c>
       <c r="B38" t="n">
-        <v>2.92</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>45658.58333333334</v>
+        <v>45659.57291666666</v>
       </c>
       <c r="B39" t="n">
-        <v>2.98</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>45658.625</v>
+        <v>45659.61458333334</v>
       </c>
       <c r="B40" t="n">
-        <v>3.09</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>45658.66666666666</v>
+        <v>45659.65625</v>
       </c>
       <c r="B41" t="n">
-        <v>3.23</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>45658.70833333334</v>
+        <v>45659.69791666666</v>
       </c>
       <c r="B42" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>45658.75</v>
+        <v>45659.73958333334</v>
       </c>
       <c r="B43" t="n">
-        <v>3.16</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>45658.79166666666</v>
+        <v>45659.78125</v>
       </c>
       <c r="B44" t="n">
-        <v>2.73</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>45658.83333333334</v>
+        <v>45659.82291666666</v>
       </c>
       <c r="B45" t="n">
-        <v>2.11</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>45658.875</v>
+        <v>45659.86458333334</v>
       </c>
       <c r="B46" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>45658.91666666666</v>
+        <v>45659.90625</v>
       </c>
       <c r="B47" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>45658.95833333334</v>
+        <v>45659.94791666666</v>
       </c>
       <c r="B48" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>45659</v>
+        <v>45659.98958333334</v>
       </c>
       <c r="B49" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -7027,7 +6627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8803,462 +8403,418 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Building_17</t>
+          <t>Building_29</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>2023</v>
       </c>
       <c r="C81" t="n">
-        <v>6467.21</v>
+        <v>6457.33</v>
       </c>
       <c r="D81" t="n">
-        <v>1397.55</v>
+        <v>1381.5</v>
       </c>
       <c r="E81" t="n">
-        <v>8777.26</v>
+        <v>8751.33</v>
       </c>
       <c r="F81" t="n">
-        <v>15.92</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Building_29</t>
+          <t>Building_48</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>2023</v>
       </c>
       <c r="C82" t="n">
-        <v>6457.33</v>
+        <v>6335.98</v>
       </c>
       <c r="D82" t="n">
-        <v>1381.5</v>
+        <v>1278</v>
       </c>
       <c r="E82" t="n">
-        <v>8751.33</v>
+        <v>8526.48</v>
       </c>
       <c r="F82" t="n">
-        <v>15.79</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Building_17</t>
+          <t>Building_48</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2024</v>
       </c>
       <c r="C83" t="n">
-        <v>6486.97</v>
+        <v>6344.78</v>
       </c>
       <c r="D83" t="n">
-        <v>1386.3</v>
+        <v>1274.1</v>
       </c>
       <c r="E83" t="n">
-        <v>8785.77</v>
+        <v>8531.379999999999</v>
       </c>
       <c r="F83" t="n">
-        <v>15.78</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Building_48</t>
+          <t>Building_28</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2023</v>
       </c>
       <c r="C84" t="n">
-        <v>6335.98</v>
+        <v>6213.92</v>
       </c>
       <c r="D84" t="n">
-        <v>1278</v>
+        <v>1182.75</v>
       </c>
       <c r="E84" t="n">
-        <v>8526.48</v>
+        <v>8309.17</v>
       </c>
       <c r="F84" t="n">
-        <v>14.99</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Building_48</t>
+          <t>Building_28</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>2024</v>
       </c>
       <c r="C85" t="n">
-        <v>6344.78</v>
+        <v>6232.09</v>
       </c>
       <c r="D85" t="n">
-        <v>1274.1</v>
+        <v>1177.05</v>
       </c>
       <c r="E85" t="n">
-        <v>8531.379999999999</v>
+        <v>8321.639999999999</v>
       </c>
       <c r="F85" t="n">
-        <v>14.93</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Building_28</t>
+          <t>Building_16</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2023</v>
       </c>
       <c r="C86" t="n">
-        <v>6213.92</v>
+        <v>6152.85</v>
       </c>
       <c r="D86" t="n">
-        <v>1182.75</v>
+        <v>1105.65</v>
       </c>
       <c r="E86" t="n">
-        <v>8309.17</v>
+        <v>8171</v>
       </c>
       <c r="F86" t="n">
-        <v>14.23</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Building_28</t>
+          <t>Building_16</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>2024</v>
       </c>
       <c r="C87" t="n">
-        <v>6232.09</v>
+        <v>6167.79</v>
       </c>
       <c r="D87" t="n">
-        <v>1177.05</v>
+        <v>1105.5</v>
       </c>
       <c r="E87" t="n">
-        <v>8321.639999999999</v>
+        <v>8185.79</v>
       </c>
       <c r="F87" t="n">
-        <v>14.14</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Building_16</t>
+          <t>Building_6</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>2023</v>
       </c>
       <c r="C88" t="n">
-        <v>6152.85</v>
+        <v>5874.36</v>
       </c>
       <c r="D88" t="n">
-        <v>1105.65</v>
+        <v>878.25</v>
       </c>
       <c r="E88" t="n">
-        <v>8171</v>
+        <v>7665.11</v>
       </c>
       <c r="F88" t="n">
-        <v>13.53</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Building_16</t>
+          <t>Building_6</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>2024</v>
       </c>
       <c r="C89" t="n">
-        <v>6167.79</v>
+        <v>5892.47</v>
       </c>
       <c r="D89" t="n">
-        <v>1105.5</v>
+        <v>868.2</v>
       </c>
       <c r="E89" t="n">
-        <v>8185.79</v>
+        <v>7673.17</v>
       </c>
       <c r="F89" t="n">
-        <v>13.51</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Building_6</t>
+          <t>Building_39</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>2023</v>
       </c>
       <c r="C90" t="n">
-        <v>5874.36</v>
+        <v>5825.61</v>
       </c>
       <c r="D90" t="n">
-        <v>878.25</v>
+        <v>831</v>
       </c>
       <c r="E90" t="n">
-        <v>7665.11</v>
+        <v>7569.11</v>
       </c>
       <c r="F90" t="n">
-        <v>11.46</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Building_6</t>
+          <t>Building_39</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>2024</v>
       </c>
       <c r="C91" t="n">
-        <v>5892.47</v>
+        <v>5844.17</v>
       </c>
       <c r="D91" t="n">
-        <v>868.2</v>
+        <v>829.5</v>
       </c>
       <c r="E91" t="n">
-        <v>7673.17</v>
+        <v>7586.17</v>
       </c>
       <c r="F91" t="n">
-        <v>11.31</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Building_39</t>
+          <t>Building_46</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>2023</v>
       </c>
       <c r="C92" t="n">
-        <v>5825.61</v>
+        <v>5746.23</v>
       </c>
       <c r="D92" t="n">
-        <v>831</v>
+        <v>765.9</v>
       </c>
       <c r="E92" t="n">
-        <v>7569.11</v>
+        <v>7424.63</v>
       </c>
       <c r="F92" t="n">
-        <v>10.98</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Building_39</t>
+          <t>Building_46</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>2024</v>
       </c>
       <c r="C93" t="n">
-        <v>5844.17</v>
+        <v>5771.09</v>
       </c>
       <c r="D93" t="n">
-        <v>829.5</v>
+        <v>768.45</v>
       </c>
       <c r="E93" t="n">
-        <v>7586.17</v>
+        <v>7452.04</v>
       </c>
       <c r="F93" t="n">
-        <v>10.93</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Building_46</t>
+          <t>Building_43</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>2023</v>
       </c>
       <c r="C94" t="n">
-        <v>5746.23</v>
+        <v>5677.64</v>
       </c>
       <c r="D94" t="n">
-        <v>765.9</v>
+        <v>697.65</v>
       </c>
       <c r="E94" t="n">
-        <v>7424.63</v>
+        <v>7287.79</v>
       </c>
       <c r="F94" t="n">
-        <v>10.32</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Building_46</t>
+          <t>Building_43</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>2024</v>
       </c>
       <c r="C95" t="n">
-        <v>5771.09</v>
+        <v>5692.94</v>
       </c>
       <c r="D95" t="n">
-        <v>768.45</v>
+        <v>698.55</v>
       </c>
       <c r="E95" t="n">
-        <v>7452.04</v>
+        <v>7303.99</v>
       </c>
       <c r="F95" t="n">
-        <v>10.31</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Building_43</t>
+          <t>Building_26</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>2023</v>
       </c>
       <c r="C96" t="n">
-        <v>5677.64</v>
+        <v>5599.08</v>
       </c>
       <c r="D96" t="n">
-        <v>697.65</v>
+        <v>625.5</v>
       </c>
       <c r="E96" t="n">
-        <v>7287.79</v>
+        <v>7137.08</v>
       </c>
       <c r="F96" t="n">
-        <v>9.57</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Building_43</t>
+          <t>Building_26</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>2024</v>
       </c>
       <c r="C97" t="n">
-        <v>5692.94</v>
+        <v>5618.47</v>
       </c>
       <c r="D97" t="n">
-        <v>698.55</v>
+        <v>618.75</v>
       </c>
       <c r="E97" t="n">
-        <v>7303.99</v>
+        <v>7149.72</v>
       </c>
       <c r="F97" t="n">
-        <v>9.56</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Building_26</t>
+          <t>Building_44</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C98" t="n">
-        <v>5599.08</v>
+        <v>5605.74</v>
       </c>
       <c r="D98" t="n">
-        <v>625.5</v>
+        <v>616.05</v>
       </c>
       <c r="E98" t="n">
-        <v>7137.08</v>
+        <v>7134.29</v>
       </c>
       <c r="F98" t="n">
-        <v>8.76</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Building_26</t>
+          <t>Building_44</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C99" t="n">
-        <v>5618.47</v>
+        <v>5586.53</v>
       </c>
       <c r="D99" t="n">
-        <v>618.75</v>
+        <v>609.75</v>
       </c>
       <c r="E99" t="n">
-        <v>7149.72</v>
+        <v>7108.78</v>
       </c>
       <c r="F99" t="n">
-        <v>8.65</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Building_44</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C100" t="n">
-        <v>5605.74</v>
-      </c>
-      <c r="D100" t="n">
-        <v>616.05</v>
-      </c>
-      <c r="E100" t="n">
-        <v>7134.29</v>
-      </c>
-      <c r="F100" t="n">
-        <v>8.640000000000001</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Building_44</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C101" t="n">
-        <v>5586.53</v>
-      </c>
-      <c r="D101" t="n">
-        <v>609.75</v>
-      </c>
-      <c r="E101" t="n">
-        <v>7108.78</v>
-      </c>
-      <c r="F101" t="n">
         <v>8.58</v>
       </c>
     </row>
